--- a/analysis/derived_data/FT_movement_formatted-data.xlsx
+++ b/analysis/derived_data/FT_movement_formatted-data.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t xml:space="preserve">partial </t>
+          <t>partial</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
